--- a/نتایج/0150BI01.xlsx
+++ b/نتایج/0150BI01.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\H.haddadniya\RCM\نتایج\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="0150BI01" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -226,8 +231,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,9 +272,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -288,9 +291,80 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K23" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:K23"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="AssetNumber"/>
+    <tableColumn id="2" name="TagNo"/>
+    <tableColumn id="3" name="نام جز"/>
+    <tableColumn id="4" name="نوع جز"/>
+    <tableColumn id="5" name="سطح تجهیز"/>
+    <tableColumn id="6" name="پارت نامبر PN"/>
+    <tableColumn id="7" name="سریال نامبر SN"/>
+    <tableColumn id="8" name="جز بالاتر (سریال نامبر بالاسری)"/>
+    <tableColumn id="9" name="مشخصه فنی"/>
+    <tableColumn id="10" name="توضیحات"/>
+    <tableColumn id="11" name="نوع فنی"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -336,7 +410,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -368,9 +442,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,6 +477,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -577,11 +653,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K64"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -636,7 +725,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>12</v>
       </c>
@@ -656,7 +745,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>13</v>
       </c>
@@ -676,7 +765,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -696,7 +785,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -716,7 +805,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -736,7 +825,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>17</v>
       </c>
@@ -756,7 +845,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>11</v>
       </c>
@@ -776,7 +865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -796,7 +885,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -816,7 +905,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>20</v>
       </c>
@@ -836,12 +925,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>11</v>
       </c>
@@ -861,7 +950,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>11</v>
       </c>
@@ -881,7 +970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>11</v>
       </c>
@@ -901,7 +990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>11</v>
       </c>
@@ -921,7 +1010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>11</v>
       </c>
@@ -941,7 +1030,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>11</v>
       </c>
@@ -961,7 +1050,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>11</v>
       </c>
@@ -981,7 +1070,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>11</v>
       </c>
@@ -1001,7 +1090,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>11</v>
       </c>
@@ -1021,7 +1110,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>11</v>
       </c>
@@ -1041,17 +1130,17 @@
         <v>64</v>
       </c>
     </row>
-    <row r="60" spans="2:8">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="2:8">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="2:8">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
         <v>11</v>
       </c>
@@ -1071,7 +1160,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="2:8">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
         <v>11</v>
       </c>
@@ -1091,7 +1180,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="64" spans="2:8">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
         <v>11</v>
       </c>
@@ -1113,5 +1202,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>